--- a/backtest_runs/20260410_193731/by_symbol/EXIDE/EXIDE.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/EXIDE/EXIDE.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-3002.790000000004</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>96997.20999999999</v>
@@ -587,7 +587,7 @@
         <v>-7.109999999993533</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>96990.10000000001</v>
@@ -633,7 +633,7 @@
         <v>-5138.160000000002</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>91851.94</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>91851.94</v>
@@ -817,7 +817,7 @@
         <v>-2002.649999999997</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>92600.86000000002</v>
@@ -909,7 +909,7 @@
         <v>-357.8699999999978</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>93032.20000000001</v>
@@ -955,7 +955,7 @@
         <v>-3524.190000000001</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>89508.01000000001</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>89508.01000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-2384.220000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>92866.3</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>92866.3</v>
@@ -1461,7 +1461,7 @@
         <v>-2035.829999999994</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>94293.04000000002</v>
@@ -1507,7 +1507,7 @@
         <v>-587.7600000000043</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>93705.28000000001</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>93705.28000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-3116.550000000008</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>90588.73000000001</v>
